--- a/output/pdf_financials_xlsx/ALTA.xlsx
+++ b/output/pdf_financials_xlsx/ALTA.xlsx
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.597755</v>
+        <v>-0.597755</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.638669</v>
+        <v>-0.638669</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-3.772806</v>
@@ -1329,10 +1329,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.597755</v>
+        <v>-0.597755</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.638669</v>
+        <v>-0.638669</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-3.772806</v>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.597755</v>
+        <v>-0.597755</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.638669</v>
+        <v>-0.638669</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-3.772806</v>
@@ -1605,10 +1605,10 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>14.943875</v>
+        <v>-14.943875</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>21.288967</v>
+        <v>-21.288967</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>-5.389723</v>
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.597755</v>
+        <v>-0.597755</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.638669</v>
+        <v>-0.638669</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-3.772806</v>
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.597755</v>
+        <v>-0.597755</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.638669</v>
+        <v>-0.638669</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-3.772806</v>
@@ -1871,10 +1871,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -4716,43 +4716,43 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.23994</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.442535</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.13124</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.566884</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>3.469324</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>3.727674</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>3.808488</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>4.354141</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>5.012012</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>5.674134</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>6.378421</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>6.378421</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>6.840198</v>
       </c>
     </row>
     <row r="93">
@@ -5873,10 +5873,10 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-0.11656</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0.208156</v>
+        <v>0.153665</v>
       </c>
       <c r="D118" s="3" t="n">
         <v>1.56576</v>
@@ -7968,7 +7968,11 @@
           <t>Share-based payments reserve (note 11)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -8763,7 +8767,11 @@
           <t>Share-based payments reserve (note 12)</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -10342,7 +10350,11 @@
           <t>Share-based payments reserve (note 13)</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -12149,7 +12161,11 @@
           <t>Share-based payments reserve (note 14)</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -12631,7 +12647,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -13421,7 +13441,11 @@
           <t>Share-based payments reserve (note 9)</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E88" s="5" t="n">
         <v>1.23994</v>
       </c>
@@ -19863,7 +19887,11 @@
           <t>Mineral exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E172" s="5" t="n">
         <v>-0.11656</v>
       </c>
@@ -26126,13 +26154,13 @@
         </is>
       </c>
       <c r="E253" s="5" t="n">
-        <v>0.597755</v>
+        <v>-0.597755</v>
       </c>
       <c r="F253" s="5" t="n">
-        <v>0.638669</v>
+        <v>-0.638669</v>
       </c>
       <c r="G253" s="5" t="n">
-        <v>3.772806</v>
+        <v>-3.772806</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ALTA.xlsx
+++ b/output/pdf_financials_xlsx/ALTA.xlsx
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001396</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -918,34 +918,34 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.005664</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.005446</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.006306</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.002432</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.001844</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.015159</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.05136</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.072758</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.074545</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.090429</v>
       </c>
     </row>
     <row r="13">
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.597755</v>
+        <v>-0.596359</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.638669</v>
@@ -1670,34 +1670,34 @@
         <v>-3.772806</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.985769</v>
+        <v>-1.991433</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-5.065049</v>
+        <v>-5.070495</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.129551</v>
+        <v>-1.135857</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.109622</v>
+        <v>-1.112054</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.597137</v>
+        <v>-1.598981</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1.582967</v>
+        <v>-1.598126</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.780377</v>
+        <v>-1.831737</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.632573</v>
+        <v>-1.705331</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.536645</v>
+        <v>-1.61119</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-1.8031</v>
+        <v>-1.893529</v>
       </c>
     </row>
     <row r="28">
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.597755</v>
+        <v>-0.596359</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.638669</v>
@@ -1762,34 +1762,34 @@
         <v>-3.772806</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.985769</v>
+        <v>-1.991433</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-5.065049</v>
+        <v>-5.070495</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.129551</v>
+        <v>-1.135857</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.109622</v>
+        <v>-1.112054</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.597137</v>
+        <v>-1.598981</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-1.582967</v>
+        <v>-1.598126</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.780377</v>
+        <v>-1.831737</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.632573</v>
+        <v>-1.705331</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.536645</v>
+        <v>-1.61119</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-1.8031</v>
+        <v>-1.893529</v>
       </c>
     </row>
     <row r="30">
@@ -1996,13 +1996,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.043664</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.289317</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.39733</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>2.179038</v>
@@ -2023,16 +2023,16 @@
         <v>5.499276</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.57608</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>4.69395</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.753617</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>7.518868</v>
       </c>
     </row>
     <row r="35">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.043664</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.289317</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.39733</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>2.238659</v>
@@ -2115,16 +2115,16 @@
         <v>5.499276</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.57608</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>4.69395</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.753617</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>7.518868</v>
       </c>
     </row>
     <row r="37">
@@ -2640,13 +2640,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.043664</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.443274</v>
+        <v>0.153957</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.690588</v>
+        <v>0.293258</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0</v>
@@ -2667,16 +2667,16 @@
         <v>0.036089</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.598909</v>
+        <v>0.022829</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>4.815862</v>
+        <v>0.121912</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.788492</v>
+        <v>0.034875</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>7.63706</v>
+        <v>0.118192</v>
       </c>
     </row>
     <row r="49">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -7465,7 +7465,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E10" s="5" t="n">
         <v>0.015</v>
       </c>
@@ -10579,7 +10583,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
@@ -12321,7 +12325,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -21022,7 +21026,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E187" s="5" t="n">
@@ -21087,7 +21091,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">

--- a/output/pdf_financials_xlsx/ALTA.xlsx
+++ b/output/pdf_financials_xlsx/ALTA.xlsx
@@ -5609,7 +5609,7 @@
         <v>0</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.033762</v>
       </c>
       <c r="G112" s="3" t="n">
         <v>0</v>
@@ -18141,7 +18141,11 @@
           <t>Proceeds from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ALTA.xlsx
+++ b/output/pdf_financials_xlsx/ALTA.xlsx
@@ -1099,10 +1099,10 @@
         <v>-0.638669</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-3.772806</v>
+        <v>-3.773682</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-1.985769</v>
+        <v>-1.967587</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>-5.065049</v>
@@ -1145,10 +1145,10 @@
         <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>0.000876</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.018182</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-0</v>
@@ -1667,10 +1667,10 @@
         <v>-0.638669</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.772806</v>
+        <v>-3.773682</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.991433</v>
+        <v>-1.973251</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-5.070495</v>
@@ -1759,10 +1759,10 @@
         <v>-0.638669</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.772806</v>
+        <v>-3.773682</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.991433</v>
+        <v>-1.973251</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-5.070495</v>
@@ -1877,10 +1877,10 @@
         <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.02321340271914804</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.9240760383149513</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-0</v>
@@ -5091,10 +5091,10 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.002531</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.019466</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>-0.253901</v>
@@ -5750,7 +5750,7 @@
         <v>0</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.093239</v>
       </c>
       <c r="H115" s="3" t="n">
         <v>0</v>
@@ -17120,7 +17120,11 @@
           <t>Shares issued for cash, private placement</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -17825,7 +17829,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -17906,7 +17914,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
@@ -19741,7 +19753,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E170" s="5" t="n">
         <v>-0.002531</v>
       </c>
@@ -24149,7 +24165,11 @@
           <t>Income tax recovery (note 20)</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
           <t>-</t>
@@ -25273,7 +25293,11 @@
           <t>Income tax recovery (expense)</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr">
         <is>
           <t>-</t>
